--- a/captax/data/outputs/Current-Law/uniformity/supplemental_table_tax_wedges_Current-Law_uniformity.xlsx
+++ b/captax/data/outputs/Current-Law/uniformity/supplemental_table_tax_wedges_Current-Law_uniformity.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="22">
   <si>
     <t>Differences in Tax Wedges Among Types of New Investment, by Tax Year</t>
   </si>
@@ -485,24 +485,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A5:M48"/>
+  <dimension ref="A5:V48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="65.7109375" customWidth="1"/>
-    <col min="2" max="13" width="9.7109375" style="1" customWidth="1"/>
+    <col min="2" max="22" width="9.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:21">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:21">
       <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:21">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -515,43 +515,79 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+    </row>
+    <row r="9" spans="1:21">
       <c r="B9" s="5">
+        <v>2016</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2017</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2018</v>
+      </c>
+      <c r="E9" s="5">
+        <v>2019</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2020</v>
+      </c>
+      <c r="G9" s="5">
+        <v>2021</v>
+      </c>
+      <c r="H9" s="5">
+        <v>2022</v>
+      </c>
+      <c r="I9" s="5">
+        <v>2023</v>
+      </c>
+      <c r="J9" s="5">
+        <v>2024</v>
+      </c>
+      <c r="K9" s="5">
         <v>2025</v>
       </c>
-      <c r="C9" s="5">
+      <c r="L9" s="5">
         <v>2026</v>
       </c>
-      <c r="D9" s="5">
+      <c r="M9" s="5">
         <v>2027</v>
       </c>
-      <c r="E9" s="5">
+      <c r="N9" s="5">
         <v>2028</v>
       </c>
-      <c r="F9" s="5">
+      <c r="O9" s="5">
         <v>2029</v>
       </c>
-      <c r="G9" s="5">
+      <c r="P9" s="5">
         <v>2030</v>
       </c>
-      <c r="H9" s="5">
+      <c r="Q9" s="5">
         <v>2031</v>
       </c>
-      <c r="I9" s="5">
+      <c r="R9" s="5">
         <v>2032</v>
       </c>
-      <c r="J9" s="5">
+      <c r="S9" s="5">
         <v>2033</v>
       </c>
-      <c r="K9" s="5">
+      <c r="T9" s="5">
         <v>2034</v>
       </c>
-      <c r="L9" s="5">
+      <c r="U9" s="5">
         <v>2035</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:21">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -564,127 +600,217 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="1">
+        <v>1.31</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1.32</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.91</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.93</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1.05</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.1</v>
       </c>
-      <c r="C11" s="1">
+      <c r="L11" s="1">
         <v>1.23</v>
       </c>
-      <c r="D11" s="1">
+      <c r="M11" s="1">
         <v>1.29</v>
       </c>
-      <c r="E11" s="1">
+      <c r="N11" s="1">
         <v>1.3</v>
       </c>
-      <c r="F11" s="1">
+      <c r="O11" s="1">
         <v>1.3</v>
       </c>
-      <c r="G11" s="1">
+      <c r="P11" s="1">
         <v>1.32</v>
       </c>
-      <c r="H11" s="1">
+      <c r="Q11" s="1">
         <v>1.32</v>
       </c>
-      <c r="I11" s="1">
+      <c r="R11" s="1">
         <v>1.32</v>
       </c>
-      <c r="J11" s="1">
+      <c r="S11" s="1">
         <v>1.32</v>
       </c>
-      <c r="K11" s="1">
+      <c r="T11" s="1">
         <v>1.32</v>
       </c>
-      <c r="L11" s="1">
+      <c r="U11" s="1">
         <v>1.32</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:21">
       <c r="A13" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:21">
       <c r="A14" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B14" s="1">
+        <v>2.04</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.05</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1.24</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1.23</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1.24</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1.29</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1.36</v>
+      </c>
+      <c r="K14" s="1">
         <v>1.42</v>
       </c>
-      <c r="C14" s="1">
+      <c r="L14" s="1">
         <v>1.59</v>
       </c>
-      <c r="D14" s="1">
+      <c r="M14" s="1">
         <v>1.66</v>
       </c>
-      <c r="E14" s="1">
+      <c r="N14" s="1">
         <v>1.65</v>
       </c>
-      <c r="F14" s="1">
+      <c r="O14" s="1">
         <v>1.65</v>
       </c>
-      <c r="G14" s="1">
+      <c r="P14" s="1">
         <v>1.67</v>
       </c>
-      <c r="H14" s="1">
+      <c r="Q14" s="1">
         <v>1.67</v>
       </c>
-      <c r="I14" s="1">
+      <c r="R14" s="1">
         <v>1.67</v>
       </c>
-      <c r="J14" s="1">
+      <c r="S14" s="1">
         <v>1.67</v>
       </c>
-      <c r="K14" s="1">
+      <c r="T14" s="1">
         <v>1.67</v>
       </c>
-      <c r="L14" s="1">
+      <c r="U14" s="1">
         <v>1.67</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:21">
       <c r="A15" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="1">
+        <v>-0.21</v>
+      </c>
+      <c r="C15" s="1">
+        <v>-0.2</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="K15" s="1">
         <v>0.44</v>
       </c>
-      <c r="C15" s="1">
+      <c r="L15" s="1">
         <v>0.46</v>
       </c>
-      <c r="D15" s="1">
+      <c r="M15" s="1">
         <v>0.54</v>
       </c>
-      <c r="E15" s="1">
+      <c r="N15" s="1">
         <v>0.5600000000000001</v>
       </c>
-      <c r="F15" s="1">
+      <c r="O15" s="1">
         <v>0.58</v>
       </c>
-      <c r="G15" s="1">
+      <c r="P15" s="1">
         <v>0.6</v>
       </c>
-      <c r="H15" s="1">
+      <c r="Q15" s="1">
         <v>0.6</v>
       </c>
-      <c r="I15" s="1">
+      <c r="R15" s="1">
         <v>0.6</v>
       </c>
-      <c r="J15" s="1">
+      <c r="S15" s="1">
         <v>0.6</v>
       </c>
-      <c r="K15" s="1">
+      <c r="T15" s="1">
         <v>0.59</v>
       </c>
-      <c r="L15" s="1">
+      <c r="U15" s="1">
         <v>0.59</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="3.75" customHeight="1">
+    <row r="16" spans="1:21" ht="3.75" customHeight="1">
       <c r="B16" s="8" t="s">
         <v>2</v>
       </c>
@@ -718,127 +844,235 @@
       <c r="L16" s="8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="M16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="S16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="T16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="U16" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B17" s="1">
+        <v>2.25</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.25</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="J17" s="1">
         <v>0.98</v>
       </c>
-      <c r="C17" s="1">
+      <c r="K17" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="L17" s="1">
         <v>1.13</v>
       </c>
-      <c r="D17" s="1">
+      <c r="M17" s="1">
         <v>1.11</v>
       </c>
-      <c r="E17" s="1">
+      <c r="N17" s="1">
         <v>1.09</v>
       </c>
-      <c r="F17" s="1">
+      <c r="O17" s="1">
         <v>1.08</v>
       </c>
-      <c r="G17" s="1">
+      <c r="P17" s="1">
         <v>1.06</v>
       </c>
-      <c r="H17" s="1">
+      <c r="Q17" s="1">
         <v>1.07</v>
       </c>
-      <c r="I17" s="1">
+      <c r="R17" s="1">
         <v>1.07</v>
       </c>
-      <c r="J17" s="1">
+      <c r="S17" s="1">
         <v>1.07</v>
       </c>
-      <c r="K17" s="1">
+      <c r="T17" s="1">
         <v>1.08</v>
       </c>
-      <c r="L17" s="1">
+      <c r="U17" s="1">
         <v>1.08</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:21">
       <c r="A19" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:21">
       <c r="A20" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B20" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1.08</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1.05</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1.07</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1.13</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1.13</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1.11</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1.18</v>
+      </c>
+      <c r="K20" s="1">
         <v>1.23</v>
       </c>
-      <c r="C20" s="1">
+      <c r="L20" s="1">
         <v>1.29</v>
       </c>
-      <c r="D20" s="1">
+      <c r="M20" s="1">
         <v>1.35</v>
       </c>
-      <c r="E20" s="1">
+      <c r="N20" s="1">
         <v>1.35</v>
       </c>
-      <c r="F20" s="1">
+      <c r="O20" s="1">
         <v>1.36</v>
       </c>
-      <c r="G20" s="1">
+      <c r="P20" s="1">
         <v>1.37</v>
       </c>
-      <c r="H20" s="1">
+      <c r="Q20" s="1">
         <v>1.37</v>
       </c>
-      <c r="I20" s="1">
+      <c r="R20" s="1">
         <v>1.38</v>
       </c>
-      <c r="J20" s="1">
+      <c r="S20" s="1">
         <v>1.38</v>
       </c>
-      <c r="K20" s="1">
+      <c r="T20" s="1">
         <v>1.38</v>
       </c>
-      <c r="L20" s="1">
+      <c r="U20" s="1">
         <v>1.38</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:21">
       <c r="A21" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B21" s="1">
+        <v>0.84</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K21" s="1">
         <v>0.87</v>
       </c>
-      <c r="C21" s="1">
+      <c r="L21" s="1">
         <v>1.11</v>
       </c>
-      <c r="D21" s="1">
+      <c r="M21" s="1">
         <v>1.2</v>
       </c>
-      <c r="E21" s="1">
+      <c r="N21" s="1">
         <v>1.2</v>
       </c>
-      <c r="F21" s="1">
+      <c r="O21" s="1">
         <v>1.21</v>
       </c>
-      <c r="G21" s="1">
+      <c r="P21" s="1">
         <v>1.23</v>
       </c>
-      <c r="H21" s="1">
+      <c r="Q21" s="1">
         <v>1.22</v>
       </c>
-      <c r="I21" s="1">
+      <c r="R21" s="1">
         <v>1.22</v>
       </c>
-      <c r="J21" s="1">
+      <c r="S21" s="1">
         <v>1.22</v>
       </c>
-      <c r="K21" s="1">
+      <c r="T21" s="1">
         <v>1.22</v>
       </c>
-      <c r="L21" s="1">
+      <c r="U21" s="1">
         <v>1.22</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="3.75" customHeight="1">
+    <row r="22" spans="1:21" ht="3.75" customHeight="1">
       <c r="B22" s="8" t="s">
         <v>2</v>
       </c>
@@ -872,279 +1106,495 @@
       <c r="L22" s="8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="M22" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="P22" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q22" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="R22" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="S22" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="T22" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="U22" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B23" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0.38</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="K23" s="1">
         <v>0.36</v>
       </c>
-      <c r="C23" s="1">
+      <c r="L23" s="1">
         <v>0.18</v>
       </c>
-      <c r="D23" s="1">
+      <c r="M23" s="1">
         <v>0.15</v>
       </c>
-      <c r="E23" s="1">
+      <c r="N23" s="1">
         <v>0.15</v>
       </c>
-      <c r="F23" s="1">
+      <c r="O23" s="1">
         <v>0.15</v>
       </c>
-      <c r="G23" s="1">
+      <c r="P23" s="1">
         <v>0.15</v>
       </c>
-      <c r="H23" s="1">
+      <c r="Q23" s="1">
         <v>0.15</v>
       </c>
-      <c r="I23" s="1">
+      <c r="R23" s="1">
         <v>0.16</v>
       </c>
-      <c r="J23" s="1">
+      <c r="S23" s="1">
         <v>0.15</v>
       </c>
-      <c r="K23" s="1">
+      <c r="T23" s="1">
         <v>0.16</v>
       </c>
-      <c r="L23" s="1">
+      <c r="U23" s="1">
         <v>0.16</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:21">
       <c r="A25" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B25" s="1">
+        <v>1.19</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="K25" s="1">
         <v>0.8</v>
       </c>
-      <c r="C25" s="1">
+      <c r="L25" s="1">
         <v>0.8</v>
       </c>
-      <c r="D25" s="1">
+      <c r="M25" s="1">
         <v>0.74</v>
       </c>
-      <c r="E25" s="1">
+      <c r="N25" s="1">
         <v>0.74</v>
       </c>
-      <c r="F25" s="1">
+      <c r="O25" s="1">
         <v>0.74</v>
       </c>
-      <c r="G25" s="1">
+      <c r="P25" s="1">
         <v>0.74</v>
       </c>
-      <c r="H25" s="1">
+      <c r="Q25" s="1">
         <v>0.74</v>
       </c>
-      <c r="I25" s="1">
+      <c r="R25" s="1">
         <v>0.74</v>
       </c>
-      <c r="J25" s="1">
+      <c r="S25" s="1">
         <v>0.74</v>
       </c>
-      <c r="K25" s="1">
+      <c r="T25" s="1">
         <v>0.74</v>
       </c>
-      <c r="L25" s="1">
+      <c r="U25" s="1">
         <v>0.74</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:21">
       <c r="A26" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B26" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="I26" s="1">
         <v>0.08</v>
       </c>
-      <c r="C26" s="1">
+      <c r="J26" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="L26" s="1">
         <v>0.09</v>
       </c>
-      <c r="D26" s="1">
+      <c r="M26" s="1">
         <v>0.06</v>
       </c>
-      <c r="E26" s="1">
+      <c r="N26" s="1">
         <v>0.05</v>
       </c>
-      <c r="F26" s="1">
+      <c r="O26" s="1">
         <v>0.04</v>
       </c>
-      <c r="G26" s="1">
+      <c r="P26" s="1">
         <v>0.03</v>
       </c>
-      <c r="H26" s="1">
+      <c r="Q26" s="1">
         <v>0.03</v>
       </c>
-      <c r="I26" s="1">
+      <c r="R26" s="1">
         <v>0.03</v>
       </c>
-      <c r="J26" s="1">
+      <c r="S26" s="1">
         <v>0.03</v>
       </c>
-      <c r="K26" s="1">
+      <c r="T26" s="1">
         <v>0.03</v>
       </c>
-      <c r="L26" s="1">
+      <c r="U26" s="1">
         <v>0.03</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:21">
       <c r="A28" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B28" s="1">
+        <v>-0.4</v>
+      </c>
+      <c r="C28" s="1">
+        <v>-0.41</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="K28" s="1">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C28" s="1">
+      <c r="L28" s="1">
         <v>-0.44</v>
       </c>
-      <c r="D28" s="1">
+      <c r="M28" s="1">
         <v>-0.45</v>
       </c>
-      <c r="E28" s="1">
+      <c r="N28" s="1">
         <v>-0.45</v>
       </c>
-      <c r="F28" s="1">
+      <c r="O28" s="1">
         <v>-0.45</v>
       </c>
-      <c r="G28" s="1">
+      <c r="P28" s="1">
         <v>-0.46</v>
       </c>
-      <c r="H28" s="1">
+      <c r="Q28" s="1">
         <v>-0.46</v>
       </c>
-      <c r="I28" s="1">
+      <c r="R28" s="1">
         <v>-0.46</v>
       </c>
-      <c r="J28" s="1">
+      <c r="S28" s="1">
         <v>-0.47</v>
       </c>
-      <c r="K28" s="1">
+      <c r="T28" s="1">
         <v>-0.47</v>
       </c>
-      <c r="L28" s="1">
+      <c r="U28" s="1">
         <v>-0.47</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:21">
       <c r="A29" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B29" s="1">
+        <v>-1.71</v>
+      </c>
+      <c r="C29" s="1">
+        <v>-1.74</v>
+      </c>
+      <c r="D29" s="1">
+        <v>-0.86</v>
+      </c>
+      <c r="E29" s="1">
+        <v>-0.86</v>
+      </c>
+      <c r="F29" s="1">
+        <v>-0.85</v>
+      </c>
+      <c r="G29" s="1">
+        <v>-0.87</v>
+      </c>
+      <c r="H29" s="1">
+        <v>-0.87</v>
+      </c>
+      <c r="I29" s="1">
+        <v>-0.85</v>
+      </c>
+      <c r="J29" s="1">
+        <v>-0.93</v>
+      </c>
+      <c r="K29" s="1">
         <v>-1.02</v>
       </c>
-      <c r="C29" s="1">
+      <c r="L29" s="1">
         <v>-1.66</v>
       </c>
-      <c r="D29" s="1">
+      <c r="M29" s="1">
         <v>-1.74</v>
       </c>
-      <c r="E29" s="1">
+      <c r="N29" s="1">
         <v>-1.75</v>
       </c>
-      <c r="F29" s="1">
+      <c r="O29" s="1">
         <v>-1.76</v>
       </c>
-      <c r="G29" s="1">
+      <c r="P29" s="1">
         <v>-1.78</v>
       </c>
-      <c r="H29" s="1">
+      <c r="Q29" s="1">
         <v>-1.78</v>
       </c>
-      <c r="I29" s="1">
+      <c r="R29" s="1">
         <v>-1.78</v>
       </c>
-      <c r="J29" s="1">
+      <c r="S29" s="1">
         <v>-1.79</v>
       </c>
-      <c r="K29" s="1">
+      <c r="T29" s="1">
         <v>-1.79</v>
       </c>
-      <c r="L29" s="1">
+      <c r="U29" s="1">
         <v>-1.79</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:21">
       <c r="A31" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:21">
       <c r="A32" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B32" s="1">
-        <v>-0.01</v>
+        <v>-0.18</v>
       </c>
       <c r="C32" s="1">
         <v>-0.19</v>
       </c>
       <c r="D32" s="1">
+        <v>-0.02</v>
+      </c>
+      <c r="E32" s="1">
+        <v>-0.02</v>
+      </c>
+      <c r="F32" s="1">
+        <v>-0.02</v>
+      </c>
+      <c r="G32" s="1">
+        <v>-0.02</v>
+      </c>
+      <c r="H32" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="I32" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="J32" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="K32" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="L32" s="1">
+        <v>-0.19</v>
+      </c>
+      <c r="M32" s="1">
         <v>-0.2</v>
       </c>
-      <c r="E32" s="1">
+      <c r="N32" s="1">
         <v>-0.2</v>
       </c>
-      <c r="F32" s="1">
+      <c r="O32" s="1">
         <v>-0.2</v>
       </c>
-      <c r="G32" s="1">
+      <c r="P32" s="1">
         <v>-0.2</v>
       </c>
-      <c r="H32" s="1">
+      <c r="Q32" s="1">
         <v>-0.2</v>
       </c>
-      <c r="I32" s="1">
+      <c r="R32" s="1">
         <v>-0.2</v>
       </c>
-      <c r="J32" s="1">
+      <c r="S32" s="1">
         <v>-0.2</v>
       </c>
-      <c r="K32" s="1">
+      <c r="T32" s="1">
         <v>-0.2</v>
       </c>
-      <c r="L32" s="1">
+      <c r="U32" s="1">
         <v>-0.2</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:21">
       <c r="A33" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="1">
+        <v>-0.77</v>
+      </c>
+      <c r="C33" s="1">
+        <v>-0.8</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0.38</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="K33" s="1">
         <v>0.23</v>
       </c>
-      <c r="C33" s="1">
+      <c r="L33" s="1">
         <v>-0.86</v>
       </c>
-      <c r="D33" s="1">
+      <c r="M33" s="1">
         <v>-0.88</v>
       </c>
-      <c r="E33" s="1">
+      <c r="N33" s="1">
         <v>-0.89</v>
       </c>
-      <c r="F33" s="1">
+      <c r="O33" s="1">
         <v>-0.9</v>
       </c>
-      <c r="G33" s="1">
+      <c r="P33" s="1">
         <v>-0.91</v>
       </c>
-      <c r="H33" s="1">
+      <c r="Q33" s="1">
         <v>-0.92</v>
       </c>
-      <c r="I33" s="1">
+      <c r="R33" s="1">
         <v>-0.92</v>
       </c>
-      <c r="J33" s="1">
+      <c r="S33" s="1">
         <v>-0.93</v>
       </c>
-      <c r="K33" s="1">
+      <c r="T33" s="1">
         <v>-0.93</v>
       </c>
-      <c r="L33" s="1">
+      <c r="U33" s="1">
         <v>-0.93</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="3.75" customHeight="1">
+    <row r="34" spans="1:21" ht="3.75" customHeight="1">
       <c r="B34" s="8" t="s">
         <v>2</v>
       </c>
@@ -1178,127 +1628,235 @@
       <c r="L34" s="8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:12">
+      <c r="M34" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N34" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="O34" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="P34" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="R34" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="S34" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="T34" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="U34" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
       <c r="A35" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B35" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="D35" s="1">
+        <v>-0.26</v>
+      </c>
+      <c r="E35" s="1">
+        <v>-0.17</v>
+      </c>
+      <c r="F35" s="1">
+        <v>-0.28</v>
+      </c>
+      <c r="G35" s="1">
+        <v>-0.38</v>
+      </c>
+      <c r="H35" s="1">
+        <v>-0.39</v>
+      </c>
+      <c r="I35" s="1">
+        <v>-0.37</v>
+      </c>
+      <c r="J35" s="1">
+        <v>-0.35</v>
+      </c>
+      <c r="K35" s="1">
         <v>-0.24</v>
       </c>
-      <c r="C35" s="1">
+      <c r="L35" s="1">
         <v>0.66</v>
       </c>
-      <c r="D35" s="1">
+      <c r="M35" s="1">
         <v>0.6899999999999999</v>
       </c>
-      <c r="E35" s="1">
+      <c r="N35" s="1">
         <v>0.7</v>
       </c>
-      <c r="F35" s="1">
+      <c r="O35" s="1">
         <v>0.7</v>
       </c>
-      <c r="G35" s="1">
+      <c r="P35" s="1">
         <v>0.71</v>
       </c>
-      <c r="H35" s="1">
+      <c r="Q35" s="1">
         <v>0.72</v>
       </c>
-      <c r="I35" s="1">
+      <c r="R35" s="1">
         <v>0.72</v>
       </c>
-      <c r="J35" s="1">
+      <c r="S35" s="1">
         <v>0.73</v>
       </c>
-      <c r="K35" s="1">
+      <c r="T35" s="1">
         <v>0.73</v>
       </c>
-      <c r="L35" s="1">
+      <c r="U35" s="1">
         <v>0.73</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:21">
       <c r="A37" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:21">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B38" s="1">
+        <v>-0.4</v>
+      </c>
+      <c r="C38" s="1">
+        <v>-0.41</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="K38" s="1">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C38" s="1">
+      <c r="L38" s="1">
         <v>-0.44</v>
       </c>
-      <c r="D38" s="1">
+      <c r="M38" s="1">
         <v>-0.45</v>
       </c>
-      <c r="E38" s="1">
+      <c r="N38" s="1">
         <v>-0.45</v>
       </c>
-      <c r="F38" s="1">
+      <c r="O38" s="1">
         <v>-0.45</v>
       </c>
-      <c r="G38" s="1">
+      <c r="P38" s="1">
         <v>-0.46</v>
       </c>
-      <c r="H38" s="1">
+      <c r="Q38" s="1">
         <v>-0.46</v>
       </c>
-      <c r="I38" s="1">
+      <c r="R38" s="1">
         <v>-0.46</v>
       </c>
-      <c r="J38" s="1">
+      <c r="S38" s="1">
         <v>-0.47</v>
       </c>
-      <c r="K38" s="1">
+      <c r="T38" s="1">
         <v>-0.47</v>
       </c>
-      <c r="L38" s="1">
+      <c r="U38" s="1">
         <v>-0.47</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:21">
       <c r="A39" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B39" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="C39" s="1">
+        <v>1.71</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1.31</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="F39" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="G39" s="1">
+        <v>1.37</v>
+      </c>
+      <c r="H39" s="1">
         <v>1.35</v>
       </c>
-      <c r="C39" s="1">
+      <c r="I39" s="1">
+        <v>1.31</v>
+      </c>
+      <c r="J39" s="1">
+        <v>1.34</v>
+      </c>
+      <c r="K39" s="1">
+        <v>1.35</v>
+      </c>
+      <c r="L39" s="1">
         <v>1.44</v>
       </c>
-      <c r="D39" s="1">
+      <c r="M39" s="1">
         <v>1.44</v>
       </c>
-      <c r="E39" s="1">
+      <c r="N39" s="1">
         <v>1.45</v>
       </c>
-      <c r="F39" s="1">
+      <c r="O39" s="1">
         <v>1.45</v>
       </c>
-      <c r="G39" s="1">
+      <c r="P39" s="1">
         <v>1.46</v>
       </c>
-      <c r="H39" s="1">
+      <c r="Q39" s="1">
         <v>1.46</v>
       </c>
-      <c r="I39" s="1">
+      <c r="R39" s="1">
         <v>1.46</v>
       </c>
-      <c r="J39" s="1">
+      <c r="S39" s="1">
         <v>1.46</v>
       </c>
-      <c r="K39" s="1">
+      <c r="T39" s="1">
         <v>1.46</v>
       </c>
-      <c r="L39" s="1">
+      <c r="U39" s="1">
         <v>1.46</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="3.75" customHeight="1">
+    <row r="40" spans="1:21" ht="3.75" customHeight="1">
       <c r="B40" s="8" t="s">
         <v>2</v>
       </c>
@@ -1332,46 +1890,100 @@
       <c r="L40" s="8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:12">
+      <c r="M40" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N40" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="O40" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="P40" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q40" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="R40" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="S40" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="T40" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="U40" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
       <c r="A41" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B41" s="1">
+        <v>-2.1</v>
+      </c>
+      <c r="C41" s="1">
+        <v>-2.12</v>
+      </c>
+      <c r="D41" s="1">
+        <v>-1.23</v>
+      </c>
+      <c r="E41" s="1">
+        <v>-1.23</v>
+      </c>
+      <c r="F41" s="1">
+        <v>-1.22</v>
+      </c>
+      <c r="G41" s="1">
+        <v>-1.24</v>
+      </c>
+      <c r="H41" s="1">
+        <v>-1.22</v>
+      </c>
+      <c r="I41" s="1">
+        <v>-1.18</v>
+      </c>
+      <c r="J41" s="1">
+        <v>-1.22</v>
+      </c>
+      <c r="K41" s="1">
         <v>-1.27</v>
       </c>
-      <c r="C41" s="1">
+      <c r="L41" s="1">
         <v>-1.88</v>
       </c>
-      <c r="D41" s="1">
+      <c r="M41" s="1">
         <v>-1.89</v>
       </c>
-      <c r="E41" s="1">
+      <c r="N41" s="1">
         <v>-1.9</v>
       </c>
-      <c r="F41" s="1">
+      <c r="O41" s="1">
         <v>-1.9</v>
       </c>
-      <c r="G41" s="1">
+      <c r="P41" s="1">
         <v>-1.92</v>
       </c>
-      <c r="H41" s="1">
+      <c r="Q41" s="1">
         <v>-1.92</v>
       </c>
-      <c r="I41" s="1">
+      <c r="R41" s="1">
         <v>-1.92</v>
       </c>
-      <c r="J41" s="1">
+      <c r="S41" s="1">
         <v>-1.93</v>
       </c>
-      <c r="K41" s="1">
+      <c r="T41" s="1">
         <v>-1.92</v>
       </c>
-      <c r="L41" s="1">
+      <c r="U41" s="1">
         <v>-1.92</v>
       </c>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" spans="1:21">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1384,18 +1996,27 @@
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
-    </row>
-    <row r="44" spans="1:12">
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="4"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="4"/>
+      <c r="T43" s="4"/>
+      <c r="U43" s="4"/>
+    </row>
+    <row r="44" spans="1:21">
       <c r="A44" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:21">
       <c r="A46" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:21">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -1408,6 +2029,15 @@
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4"/>
+      <c r="R48" s="4"/>
+      <c r="S48" s="4"/>
+      <c r="T48" s="4"/>
+      <c r="U48" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B11:L38">

--- a/captax/data/outputs/Current-Law/uniformity/supplemental_table_tax_wedges_Current-Law_uniformity.xlsx
+++ b/captax/data/outputs/Current-Law/uniformity/supplemental_table_tax_wedges_Current-Law_uniformity.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED75995B-B6BA-434E-94D9-25D5B76A3150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="29880" yWindow="1080" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Differences in Tax Wedges" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -85,12 +86,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0_)"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,20 +191,28 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;*&quot;;&quot;*&quot;"/>
+      <numFmt numFmtId="167" formatCode="&quot;**&quot;;&quot;**&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;**&quot;;&quot;**&quot;"/>
+      <numFmt numFmtId="166" formatCode="&quot;*&quot;;&quot;*&quot;"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -241,7 +250,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -275,6 +284,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -309,9 +319,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -484,25 +495,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A5:M48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="65.7109375" customWidth="1"/>
     <col min="2" max="13" width="9.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -516,42 +527,42 @@
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C9" s="5">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="D9" s="5">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E9" s="5">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="F9" s="5">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="G9" s="5">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="H9" s="5">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="I9" s="5">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="J9" s="5">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="K9" s="5">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="L9" s="5">
-        <v>2035</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -565,126 +576,126 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="1">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="C11" s="1">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="E11" s="1">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F11" s="1">
-        <v>1.3</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="G11" s="1">
-        <v>1.32</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>1.32</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="I11" s="1">
-        <v>1.32</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="J11" s="1">
-        <v>1.32</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="K11" s="1">
-        <v>1.32</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="L11" s="1">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B14" s="1">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="C14" s="1">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="D14" s="1">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="E14" s="1">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="F14" s="1">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="G14" s="1">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="H14" s="1">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="I14" s="1">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="J14" s="1">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="K14" s="1">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="L14" s="1">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="I15" s="1">
         <v>0.44</v>
       </c>
-      <c r="C15" s="1">
-        <v>0.46</v>
-      </c>
-      <c r="D15" s="1">
-        <v>0.54</v>
-      </c>
-      <c r="E15" s="1">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0.58</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="I15" s="1">
-        <v>0.6</v>
-      </c>
       <c r="J15" s="1">
-        <v>0.6</v>
+        <v>0.44</v>
       </c>
       <c r="K15" s="1">
-        <v>0.59</v>
+        <v>0.44</v>
       </c>
       <c r="L15" s="1">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="3.75" customHeight="1">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="8" t="s">
         <v>2</v>
       </c>
@@ -719,126 +730,126 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B17" s="1">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="C17" s="1">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="D17" s="1">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="E17" s="1">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="F17" s="1">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="G17" s="1">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="H17" s="1">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="I17" s="1">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="J17" s="1">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="L17" s="1">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B20" s="1">
-        <v>1.23</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="C20" s="1">
+        <v>1.17</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1.17</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1.26</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1.28</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1.28</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1.28</v>
+      </c>
+      <c r="L20" s="1">
         <v>1.29</v>
       </c>
-      <c r="D20" s="1">
-        <v>1.35</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1.35</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1.36</v>
-      </c>
-      <c r="G20" s="1">
-        <v>1.37</v>
-      </c>
-      <c r="H20" s="1">
-        <v>1.37</v>
-      </c>
-      <c r="I20" s="1">
-        <v>1.38</v>
-      </c>
-      <c r="J20" s="1">
-        <v>1.38</v>
-      </c>
-      <c r="K20" s="1">
-        <v>1.38</v>
-      </c>
-      <c r="L20" s="1">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B21" s="1">
-        <v>0.87</v>
+        <v>0.67</v>
       </c>
       <c r="C21" s="1">
-        <v>1.11</v>
+        <v>0.71</v>
       </c>
       <c r="D21" s="1">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="E21" s="1">
-        <v>1.2</v>
+        <v>0.83</v>
       </c>
       <c r="F21" s="1">
-        <v>1.21</v>
+        <v>0.84</v>
       </c>
       <c r="G21" s="1">
-        <v>1.23</v>
+        <v>0.84</v>
       </c>
       <c r="H21" s="1">
-        <v>1.22</v>
+        <v>0.83</v>
       </c>
       <c r="I21" s="1">
-        <v>1.22</v>
+        <v>0.84</v>
       </c>
       <c r="J21" s="1">
-        <v>1.22</v>
+        <v>0.84</v>
       </c>
       <c r="K21" s="1">
-        <v>1.22</v>
+        <v>0.84</v>
       </c>
       <c r="L21" s="1">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="3.75" customHeight="1">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="8" t="s">
         <v>2</v>
       </c>
@@ -873,278 +884,278 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B23" s="1">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="C23" s="1">
-        <v>0.18</v>
+        <v>0.46</v>
       </c>
       <c r="D23" s="1">
-        <v>0.15</v>
+        <v>0.46</v>
       </c>
       <c r="E23" s="1">
-        <v>0.15</v>
+        <v>0.43</v>
       </c>
       <c r="F23" s="1">
-        <v>0.15</v>
+        <v>0.43</v>
       </c>
       <c r="G23" s="1">
-        <v>0.15</v>
+        <v>0.43</v>
       </c>
       <c r="H23" s="1">
-        <v>0.15</v>
+        <v>0.44</v>
       </c>
       <c r="I23" s="1">
-        <v>0.16</v>
+        <v>0.44</v>
       </c>
       <c r="J23" s="1">
-        <v>0.15</v>
+        <v>0.44</v>
       </c>
       <c r="K23" s="1">
-        <v>0.16</v>
+        <v>0.44</v>
       </c>
       <c r="L23" s="1">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B25" s="1">
-        <v>0.8</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="C25" s="1">
-        <v>0.8</v>
+        <v>1.08</v>
       </c>
       <c r="D25" s="1">
-        <v>0.74</v>
+        <v>1.07</v>
       </c>
       <c r="E25" s="1">
-        <v>0.74</v>
+        <v>1.04</v>
       </c>
       <c r="F25" s="1">
-        <v>0.74</v>
+        <v>1.04</v>
       </c>
       <c r="G25" s="1">
-        <v>0.74</v>
+        <v>1.04</v>
       </c>
       <c r="H25" s="1">
-        <v>0.74</v>
+        <v>1.04</v>
       </c>
       <c r="I25" s="1">
-        <v>0.74</v>
+        <v>1.04</v>
       </c>
       <c r="J25" s="1">
-        <v>0.74</v>
+        <v>1.04</v>
       </c>
       <c r="K25" s="1">
-        <v>0.74</v>
+        <v>1.04</v>
       </c>
       <c r="L25" s="1">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B26" s="1">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="C26" s="1">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="D26" s="1">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="E26" s="1">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="F26" s="1">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G26" s="1">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H26" s="1">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="I26" s="1">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J26" s="1">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="K26" s="1">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="L26" s="1">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B28" s="1">
-        <v>0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="C28" s="1">
-        <v>-0.44</v>
+        <v>-0.03</v>
       </c>
       <c r="D28" s="1">
-        <v>-0.45</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="E28" s="1">
-        <v>-0.45</v>
+        <v>-0.09</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.45</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G28" s="1">
-        <v>-0.46</v>
+        <v>0.06</v>
       </c>
       <c r="H28" s="1">
-        <v>-0.46</v>
+        <v>0.04</v>
       </c>
       <c r="I28" s="1">
-        <v>-0.46</v>
+        <v>0.03</v>
       </c>
       <c r="J28" s="1">
-        <v>-0.47</v>
+        <v>0.02</v>
       </c>
       <c r="K28" s="1">
-        <v>-0.47</v>
+        <v>0.02</v>
       </c>
       <c r="L28" s="1">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B29" s="1">
-        <v>-1.02</v>
+        <v>-0.97</v>
       </c>
       <c r="C29" s="1">
-        <v>-1.66</v>
+        <v>-1.04</v>
       </c>
       <c r="D29" s="1">
-        <v>-1.74</v>
+        <v>-1.08</v>
       </c>
       <c r="E29" s="1">
-        <v>-1.75</v>
+        <v>-1.2</v>
       </c>
       <c r="F29" s="1">
-        <v>-1.76</v>
+        <v>-1.04</v>
       </c>
       <c r="G29" s="1">
-        <v>-1.78</v>
+        <v>-1.06</v>
       </c>
       <c r="H29" s="1">
-        <v>-1.78</v>
+        <v>-1.07</v>
       </c>
       <c r="I29" s="1">
-        <v>-1.78</v>
+        <v>-1.08</v>
       </c>
       <c r="J29" s="1">
-        <v>-1.79</v>
+        <v>-1.0900000000000001</v>
       </c>
       <c r="K29" s="1">
-        <v>-1.79</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="L29" s="1">
-        <v>-1.79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
+        <v>-1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B32" s="1">
+        <v>-0.08</v>
+      </c>
+      <c r="C32" s="1">
+        <v>-0.08</v>
+      </c>
+      <c r="D32" s="1">
+        <v>-0.09</v>
+      </c>
+      <c r="E32" s="1">
+        <v>-0.09</v>
+      </c>
+      <c r="F32" s="1">
         <v>-0.01</v>
       </c>
-      <c r="C32" s="1">
-        <v>-0.19</v>
-      </c>
-      <c r="D32" s="1">
-        <v>-0.2</v>
-      </c>
-      <c r="E32" s="1">
-        <v>-0.2</v>
-      </c>
-      <c r="F32" s="1">
-        <v>-0.2</v>
-      </c>
       <c r="G32" s="1">
-        <v>-0.2</v>
+        <v>-0.01</v>
       </c>
       <c r="H32" s="1">
-        <v>-0.2</v>
+        <v>-0.01</v>
       </c>
       <c r="I32" s="1">
-        <v>-0.2</v>
+        <v>-0.01</v>
       </c>
       <c r="J32" s="1">
-        <v>-0.2</v>
+        <v>-0.01</v>
       </c>
       <c r="K32" s="1">
-        <v>-0.2</v>
+        <v>-0.01</v>
       </c>
       <c r="L32" s="1">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="1">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="C33" s="1">
-        <v>-0.86</v>
+        <v>0.05</v>
       </c>
       <c r="D33" s="1">
-        <v>-0.88</v>
+        <v>-0.04</v>
       </c>
       <c r="E33" s="1">
-        <v>-0.89</v>
+        <v>-0.1</v>
       </c>
       <c r="F33" s="1">
-        <v>-0.9</v>
+        <v>0.22</v>
       </c>
       <c r="G33" s="1">
-        <v>-0.91</v>
+        <v>0.18</v>
       </c>
       <c r="H33" s="1">
-        <v>-0.92</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="I33" s="1">
-        <v>-0.92</v>
+        <v>0.11</v>
       </c>
       <c r="J33" s="1">
-        <v>-0.93</v>
+        <v>0.08</v>
       </c>
       <c r="K33" s="1">
-        <v>-0.93</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="L33" s="1">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="3.75" customHeight="1">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="8" t="s">
         <v>2</v>
       </c>
@@ -1179,126 +1190,126 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B35" s="1">
-        <v>-0.24</v>
+        <v>-0.21</v>
       </c>
       <c r="C35" s="1">
-        <v>0.66</v>
+        <v>-0.14000000000000001</v>
       </c>
       <c r="D35" s="1">
-        <v>0.6899999999999999</v>
+        <v>-0.04</v>
       </c>
       <c r="E35" s="1">
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="F35" s="1">
-        <v>0.7</v>
+        <v>-0.23</v>
       </c>
       <c r="G35" s="1">
-        <v>0.71</v>
+        <v>-0.19</v>
       </c>
       <c r="H35" s="1">
-        <v>0.72</v>
+        <v>-0.15</v>
       </c>
       <c r="I35" s="1">
-        <v>0.72</v>
+        <v>-0.12</v>
       </c>
       <c r="J35" s="1">
-        <v>0.73</v>
+        <v>-0.09</v>
       </c>
       <c r="K35" s="1">
-        <v>0.73</v>
+        <v>-0.08</v>
       </c>
       <c r="L35" s="1">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B38" s="1">
-        <v>0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="C38" s="1">
-        <v>-0.44</v>
+        <v>-0.03</v>
       </c>
       <c r="D38" s="1">
-        <v>-0.45</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="E38" s="1">
-        <v>-0.45</v>
+        <v>-0.09</v>
       </c>
       <c r="F38" s="1">
-        <v>-0.45</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G38" s="1">
-        <v>-0.46</v>
+        <v>0.06</v>
       </c>
       <c r="H38" s="1">
-        <v>-0.46</v>
+        <v>0.04</v>
       </c>
       <c r="I38" s="1">
-        <v>-0.46</v>
+        <v>0.03</v>
       </c>
       <c r="J38" s="1">
-        <v>-0.47</v>
+        <v>0.02</v>
       </c>
       <c r="K38" s="1">
-        <v>-0.47</v>
+        <v>0.02</v>
       </c>
       <c r="L38" s="1">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B39" s="1">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="C39" s="1">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="D39" s="1">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="E39" s="1">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="F39" s="1">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="G39" s="1">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="H39" s="1">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="I39" s="1">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="J39" s="1">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="K39" s="1">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="L39" s="1">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="3.75" customHeight="1">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="8" t="s">
         <v>2</v>
       </c>
@@ -1333,45 +1344,45 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B41" s="1">
-        <v>-1.27</v>
+        <v>-1.51</v>
       </c>
       <c r="C41" s="1">
-        <v>-1.88</v>
+        <v>-1.55</v>
       </c>
       <c r="D41" s="1">
-        <v>-1.89</v>
+        <v>-1.58</v>
       </c>
       <c r="E41" s="1">
-        <v>-1.9</v>
+        <v>-1.61</v>
       </c>
       <c r="F41" s="1">
-        <v>-1.9</v>
+        <v>-1.45</v>
       </c>
       <c r="G41" s="1">
-        <v>-1.92</v>
+        <v>-1.46</v>
       </c>
       <c r="H41" s="1">
-        <v>-1.92</v>
+        <v>-1.47</v>
       </c>
       <c r="I41" s="1">
-        <v>-1.92</v>
+        <v>-1.49</v>
       </c>
       <c r="J41" s="1">
-        <v>-1.93</v>
+        <v>-1.5</v>
       </c>
       <c r="K41" s="1">
-        <v>-1.92</v>
+        <v>-1.51</v>
       </c>
       <c r="L41" s="1">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1385,17 +1396,17 @@
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -1411,15 +1422,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B11:L38">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
       <formula>0.001</formula>
       <formula>0.049</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="between">
       <formula>-0.049</formula>
       <formula>-0.001</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>